--- a/output/excel/pareto_metrics_5_130.xlsx
+++ b/output/excel/pareto_metrics_5_130.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
   <si>
     <t>Config</t>
   </si>
@@ -62,6 +62,9 @@
   </si>
   <si>
     <t>PSP</t>
+  </si>
+  <si>
+    <t>DQN</t>
   </si>
 </sst>
 </file>
@@ -419,7 +422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -597,6 +600,41 @@
         <v>0</v>
       </c>
     </row>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6">
+        <v>0.4595764425498613</v>
+      </c>
+      <c r="D6">
+        <v>0.3773704866727429</v>
+      </c>
+      <c r="E6">
+        <v>0.2100436430296232</v>
+      </c>
+      <c r="F6">
+        <v>0.4750689705799169</v>
+      </c>
+      <c r="G6">
+        <v>0.4750689705799169</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="J6">
+        <v>0.3959328148050926</v>
+      </c>
+      <c r="K6">
+        <v>0.2761696454303723</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
